--- a/resultados/Matrizes de Transição.xlsx
+++ b/resultados/Matrizes de Transição.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8dffaa0cd82b602/Documentos/Progamacao/R/Dados PNADC 2019-2020 - PIBIC/Git/IHPOJ/resultados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="8_{8B5E2424-CC3C-4C3B-91F1-99B01F86C9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B97FA5B-1E09-4A8E-BD64-DCA227D906CA}"/>
+  <xr:revisionPtr revIDLastSave="430" documentId="8_{8B5E2424-CC3C-4C3B-91F1-99B01F86C9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{471515A6-1B5E-44BE-BEF7-0A9C68C5543A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3559914F-9E66-4E6A-A04F-3ECA189E0862}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
   <si>
     <t>Pré-Pandemia</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Rural</t>
+  </si>
+  <si>
+    <t>Pré-pandemia</t>
+  </si>
+  <si>
+    <t>Pós-pandemia</t>
   </si>
 </sst>
 </file>
@@ -179,10 +185,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,10 +504,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F302EF2-8182-4C75-9102-CE17C7845DA8}">
-  <dimension ref="B1:AE20"/>
+  <dimension ref="B1:AE26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:31" x14ac:dyDescent="0.3">
@@ -1563,8 +1566,277 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+    </row>
+    <row r="24" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="25" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="D25" s="1">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="E25" s="1">
+        <f>1-D25</f>
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="G25" s="1">
+        <f t="shared" ref="G25:G26" si="6">1-F25</f>
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" ref="I25:I26" si="7">1-H25</f>
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="K25" s="1">
+        <f t="shared" ref="K25:K26" si="8">1-J25</f>
+        <v>0.39</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="M25" s="1">
+        <f t="shared" ref="M25:M26" si="9">1-L25</f>
+        <v>0.20699999999999996</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="O25" s="1">
+        <f t="shared" ref="O25:O26" si="10">1-N25</f>
+        <v>0.20299999999999996</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="Q25" s="1">
+        <f t="shared" ref="Q25:Q26" si="11">1-P25</f>
+        <v>0.19899999999999995</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="S25" s="1">
+        <f t="shared" ref="S25:S26" si="12">1-R25</f>
+        <v>0.22199999999999998</v>
+      </c>
+      <c r="T25" s="1">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="U25" s="1">
+        <f t="shared" ref="U25:U26" si="13">1-T25</f>
+        <v>0.45599999999999996</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="W25" s="1">
+        <f t="shared" ref="W25:W26" si="14">1-V25</f>
+        <v>0.43700000000000006</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Y25" s="1">
+        <f t="shared" ref="Y25:Y26" si="15">1-X25</f>
+        <v>0.46399999999999997</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="AA25" s="1">
+        <f t="shared" ref="AA25:AA26" si="16">1-Z25</f>
+        <v>0.46399999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="D26" s="1">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="E26" s="1">
+        <f>1-D26</f>
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="F26" s="1">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="6"/>
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="H26" s="1">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="7"/>
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="J26" s="1">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="8"/>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="L26" s="1">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="M26" s="1">
+        <f t="shared" si="9"/>
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="N26" s="1">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="O26" s="1">
+        <f t="shared" si="10"/>
+        <v>0.93399999999999994</v>
+      </c>
+      <c r="P26" s="1">
+        <v>5.5E-2</v>
+      </c>
+      <c r="Q26" s="1">
+        <f t="shared" si="11"/>
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="R26" s="1">
+        <v>5.5E-2</v>
+      </c>
+      <c r="S26" s="1">
+        <f t="shared" si="12"/>
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="T26" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="U26" s="1">
+        <f t="shared" si="13"/>
+        <v>0.96</v>
+      </c>
+      <c r="V26" s="1">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="W26" s="1">
+        <f t="shared" si="14"/>
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="X26" s="1">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="Y26" s="1">
+        <f t="shared" si="15"/>
+        <v>0.94100000000000006</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="AA26" s="1">
+        <f t="shared" si="16"/>
+        <v>0.94199999999999995</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="78">
+    <mergeCell ref="D23:K23"/>
+    <mergeCell ref="L23:S23"/>
+    <mergeCell ref="T23:AA23"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="Z24:AA24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
     <mergeCell ref="P2:U2"/>
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="R3:S3"/>
